--- a/Referensi/AR4 6DOF Manipulator/AR4-MK3 motor step calculations.xlsx
+++ b/Referensi/AR4 6DOF Manipulator/AR4-MK3 motor step calculations.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26626"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chris\Desktop\AR4-V2\AR4-V2 DOCUMENTATION\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data Udin\Kuliah\7. TUGAS AKHIR\Arm Manipulator\Referensi\AR4 6DOF Manipulator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D2B96D-C351-4D1B-92BF-7D194AAABB63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C159B3C-F861-42C8-8D5F-43BDA1EBE811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="75" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -493,7 +493,6 @@
         <v>10</v>
       </c>
       <c r="C2" s="2">
-        <f>60/15</f>
         <v>4</v>
       </c>
       <c r="D2" s="2">
